--- a/data/trans_orig/P6713-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6713-Clase-trans_orig.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2012</t>
+          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2012 (tasa de respuesta: 99,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11786</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15637</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11365</t>
+          <t>11164</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12113</t>
+          <t>11925</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,47 +894,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>10294</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>17518</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>10294</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>5026</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>18028</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>37233</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65570</t>
+          <t>63671</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28899</t>
+          <t>27369</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>51110</t>
+          <t>52085</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>83563</t>
+          <t>85565</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39406</t>
+          <t>38016</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66246</t>
+          <t>64945</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28227</t>
+          <t>28029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52577</t>
+          <t>51672</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73665</t>
+          <t>75402</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110784</t>
+          <t>111698</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174114</t>
+          <t>172617</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>207589</t>
+          <t>206989</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>114460</t>
+          <t>113484</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>142845</t>
+          <t>142971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>295041</t>
+          <t>296446</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>341246</t>
+          <t>341667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,86%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2318</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12435</t>
+          <t>12311</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17184</t>
+          <t>17456</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21353</t>
+          <t>20577</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>18839</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>12182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33742</t>
+          <t>32850</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29100</t>
+          <t>29394</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>54964</t>
+          <t>55282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26218</t>
+          <t>25574</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48220</t>
+          <t>49021</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60949</t>
+          <t>60053</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>96435</t>
+          <t>95500</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53951</t>
+          <t>53811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84216</t>
+          <t>83625</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30328</t>
+          <t>31448</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53930</t>
+          <t>55171</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92906</t>
+          <t>91193</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129220</t>
+          <t>129336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115587</t>
+          <t>115643</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150100</t>
+          <t>150090</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59201</t>
+          <t>58222</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86397</t>
+          <t>85643</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>183504</t>
+          <t>184450</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>226901</t>
+          <t>229274</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>54,29%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11613</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18882</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23161</t>
+          <t>25207</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>10611</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11000</t>
+          <t>11631</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29872</t>
+          <t>30600</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34461</t>
+          <t>35906</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60273</t>
+          <t>61392</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>12963</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30007</t>
+          <t>30144</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>53178</t>
+          <t>53533</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>83706</t>
+          <t>84311</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59849</t>
+          <t>59361</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87932</t>
+          <t>88390</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>13318</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29580</t>
+          <t>29691</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77160</t>
+          <t>77728</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>110872</t>
+          <t>111446</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>120839</t>
+          <t>121554</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>157389</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48872</t>
+          <t>50561</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>70798</t>
+          <t>71368</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>180071</t>
+          <t>179612</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>221688</t>
+          <t>218116</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,06%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30068</t>
+          <t>31246</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12507</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31554</t>
+          <t>29670</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27486</t>
+          <t>28017</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54119</t>
+          <t>54222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21248</t>
+          <t>22329</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45424</t>
+          <t>46059</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27962</t>
+          <t>26554</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37304</t>
+          <t>37196</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>66018</t>
+          <t>65615</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>93649</t>
+          <t>95752</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>131844</t>
+          <t>132555</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66464</t>
+          <t>66983</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>98296</t>
+          <t>98824</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>171483</t>
+          <t>170355</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>223726</t>
+          <t>219152</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>83004</t>
+          <t>83620</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>119840</t>
+          <t>120794</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52990</t>
+          <t>53748</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82621</t>
+          <t>81332</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>145482</t>
+          <t>145143</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>192592</t>
+          <t>192783</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>143105</t>
+          <t>142048</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>182569</t>
+          <t>182691</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,49 +3244,49 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>110591</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>94299</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>127305</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>37,15%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>31,68%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>42,77%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>110591</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>93584</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>129233</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>37,15%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>31,44%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>43,42%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>258</t>
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>243664</t>
+          <t>246152</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>297431</t>
+          <t>298372</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17341</t>
+          <t>17333</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36160</t>
+          <t>36895</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18466</t>
+          <t>18226</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37857</t>
+          <t>36904</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>38939</t>
+          <t>40470</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>68173</t>
+          <t>66800</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20445</t>
+          <t>21808</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18143</t>
+          <t>18249</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38196</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27818</t>
+          <t>27145</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>51613</t>
+          <t>52876</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29230</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>52918</t>
+          <t>52084</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>30708</t>
+          <t>31730</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53849</t>
+          <t>54307</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>65471</t>
+          <t>65920</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>98937</t>
+          <t>98726</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>21265</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>42532</t>
+          <t>41713</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,82 +3813,82 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>14,08%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>27,63%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>29660</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>21039</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>39382</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>16,89%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>11,98%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>22,42%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>60497</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>48428</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>76147</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>18,52%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
           <t>14,83%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>28,17%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>29660</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>20147</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>40748</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>16,89%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>11,47%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>23,2%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>60497</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>46271</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>76489</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>18,52%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>14,17%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31092</t>
+          <t>31878</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>55086</t>
+          <t>54611</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>38812</t>
+          <t>38899</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>63638</t>
+          <t>64655</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>75721</t>
+          <t>76448</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>110858</t>
+          <t>109478</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,52%</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4131,107 +4131,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58826</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44843</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76887</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>60240</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46453</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76194</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>110</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>119067</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96706</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>139908</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -4244,107 +4244,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75679</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59406</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95850</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63767</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49205</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>80445</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>139446</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>114879</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>164835</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -4357,107 +4357,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>273</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288346</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>259390</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>319812</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>184</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>198680</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>173678</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>224700</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>457</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>487026</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>449396</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>530917</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -4470,107 +4470,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>312</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>324840</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>290681</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>357649</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>181</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>198719</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>173052</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>226030</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>493</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>523559</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>482769</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>562307</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -4583,107 +4583,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>622</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>666760</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>629882</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>707062</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>394</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>422865</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>392031</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>455033</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1089625</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1040461</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1144728</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,53%</t>
         </is>
       </c>
     </row>
@@ -4696,804 +4696,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1414451</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1414451</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1414451</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>872</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>944272</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>944272</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>944272</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2358722</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2358722</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2358722</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>58826</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>44688</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>60240</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>45780</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>77034</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>119067</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>99351</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>142515</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Solo alguna vez</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>75679</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>57682</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>95795</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>63767</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>48996</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>83273</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>139446</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>116612</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>166829</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>288346</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>258688</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>324586</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>20,39%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>22,95%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>198680</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>173078</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>225076</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>21,04%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>18,33%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>23,84%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>487026</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>448801</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>532615</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>20,65%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>19,03%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>324840</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>293788</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>358025</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>22,97%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>20,77%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>25,31%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>198719</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>173066</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>223797</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>21,04%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>18,33%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>23,7%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>523559</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>480259</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>567195</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>22,2%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>20,36%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>24,05%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>666760</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>628332</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>706236</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>47,14%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>44,42%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>49,93%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>422865</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>391805</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>456934</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>44,78%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>41,49%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>48,39%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>1089625</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>1041204</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>1136814</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>46,2%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>44,14%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>48,2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1329</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1414451</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1414451</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1414451</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>872</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>944272</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>944272</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>944272</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2201</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2358722</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2358722</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2358722</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>
@@ -5513,7 +4830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5544,7 +4861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2016</t>
+          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5744,7 +5061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5759,7 +5076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5779,7 +5096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>7364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5794,7 +5111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5809,12 +5126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>11290</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5829,7 +5146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24637</t>
+          <t>24040</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5867,12 +5184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5887,12 +5204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22442</t>
+          <t>22109</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5902,12 +5219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5922,12 +5239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40273</t>
+          <t>38973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5937,12 +5254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5282,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39333</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65910</t>
+          <t>65410</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5980,12 +5297,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6000,12 +5317,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19565</t>
+          <t>19621</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39885</t>
+          <t>39789</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6015,12 +5332,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6035,12 +5352,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>64185</t>
+          <t>62601</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96407</t>
+          <t>96841</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6050,12 +5367,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +5395,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47413</t>
+          <t>47212</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76112</t>
+          <t>76270</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6093,12 +5410,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6113,12 +5430,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>40966</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65767</t>
+          <t>66281</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6128,12 +5445,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6148,12 +5465,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>95826</t>
+          <t>94750</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134299</t>
+          <t>134371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6163,12 +5480,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +5508,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>134141</t>
+          <t>134181</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>169118</t>
+          <t>167056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6206,12 +5523,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6226,12 +5543,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102714</t>
+          <t>102416</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>132205</t>
+          <t>132076</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6241,12 +5558,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6261,12 +5578,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>243397</t>
+          <t>246302</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>291834</t>
+          <t>292431</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6276,12 +5593,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,38%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +5738,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14558</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6436,12 +5753,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6456,12 +5773,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6471,12 +5788,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6491,12 +5808,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24012</t>
+          <t>24824</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6506,12 +5823,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +5851,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15053</t>
+          <t>14544</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32690</t>
+          <t>32301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6549,12 +5866,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6569,12 +5886,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33187</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6584,12 +5901,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6604,12 +5921,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33938</t>
+          <t>33991</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59149</t>
+          <t>59579</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6619,12 +5936,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +5964,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>41007</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69977</t>
+          <t>70107</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6662,12 +5979,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6682,12 +5999,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41835</t>
+          <t>41181</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69403</t>
+          <t>66908</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6697,12 +6014,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6717,12 +6034,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90858</t>
+          <t>92610</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>128564</t>
+          <t>129466</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6732,12 +6049,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6077,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55502</t>
+          <t>53922</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84468</t>
+          <t>83518</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6775,12 +6092,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6795,12 +6112,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38536</t>
+          <t>38087</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62583</t>
+          <t>61894</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6810,12 +6127,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6830,12 +6147,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98192</t>
+          <t>99819</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134806</t>
+          <t>139606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6845,12 +6162,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6190,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76312</t>
+          <t>76168</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108400</t>
+          <t>107510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6888,12 +6205,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6908,12 +6225,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43956</t>
+          <t>44362</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68496</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6923,12 +6240,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6943,12 +6260,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128227</t>
+          <t>125485</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>170056</t>
+          <t>167997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6958,12 +6275,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +6420,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12421</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7118,12 +6435,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7143,7 +6460,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7158,7 +6475,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7173,12 +6490,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15600</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7188,12 +6505,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +6533,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>7350</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21936</t>
+          <t>22336</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7231,12 +6548,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7251,12 +6568,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>11114</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7266,12 +6583,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7286,12 +6603,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>11151</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28163</t>
+          <t>28156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7301,7 +6618,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7329,12 +6646,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41500</t>
+          <t>41625</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67840</t>
+          <t>68630</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7344,12 +6661,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7364,12 +6681,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>17750</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7379,12 +6696,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7399,12 +6716,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>50196</t>
+          <t>48746</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78248</t>
+          <t>79129</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7414,12 +6731,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +6759,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50382</t>
+          <t>51416</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76590</t>
+          <t>78096</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7457,12 +6774,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7477,12 +6794,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15165</t>
+          <t>14185</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30724</t>
+          <t>29499</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7492,12 +6809,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7512,12 +6829,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70675</t>
+          <t>70652</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103919</t>
+          <t>101565</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7527,12 +6844,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +6872,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>66301</t>
+          <t>67909</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95170</t>
+          <t>96443</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7570,12 +6887,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7590,12 +6907,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>21423</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37409</t>
+          <t>37566</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7605,12 +6922,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7625,12 +6942,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>93802</t>
+          <t>91028</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>127846</t>
+          <t>127875</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7640,12 +6957,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7102,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30748</t>
+          <t>29349</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55647</t>
+          <t>54976</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7800,12 +7117,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7820,12 +7137,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20011</t>
+          <t>20741</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40642</t>
+          <t>41738</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7835,12 +7152,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7855,12 +7172,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55729</t>
+          <t>54031</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87532</t>
+          <t>86699</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7870,12 +7187,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7215,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>46216</t>
+          <t>48197</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>76481</t>
+          <t>74969</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7913,12 +7230,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7933,12 +7250,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36978</t>
+          <t>37454</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>63020</t>
+          <t>63043</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7948,12 +7265,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7968,12 +7285,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>90710</t>
+          <t>90144</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>129913</t>
+          <t>130466</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7983,12 +7300,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +7328,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>119815</t>
+          <t>119612</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>160112</t>
+          <t>161901</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8026,12 +7343,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8046,12 +7363,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>68433</t>
+          <t>69117</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>100444</t>
+          <t>100802</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8061,12 +7378,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8081,12 +7398,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>197628</t>
+          <t>198684</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>252714</t>
+          <t>247280</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8096,12 +7413,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +7441,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111928</t>
+          <t>110008</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>152088</t>
+          <t>149005</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8139,12 +7456,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8159,12 +7476,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>98643</t>
+          <t>99850</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>135348</t>
+          <t>134581</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8174,12 +7491,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8194,12 +7511,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>218914</t>
+          <t>221697</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>272460</t>
+          <t>275206</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8209,12 +7526,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +7554,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>99325</t>
+          <t>98208</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>137562</t>
+          <t>136338</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8252,12 +7569,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8272,12 +7589,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>72853</t>
+          <t>74983</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>104683</t>
+          <t>107777</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8287,12 +7604,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8307,12 +7624,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>182374</t>
+          <t>182305</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>230527</t>
+          <t>233027</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8322,12 +7639,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +7784,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>17185</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37516</t>
+          <t>37528</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8482,12 +7799,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8502,12 +7819,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39569</t>
+          <t>39917</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>64696</t>
+          <t>63694</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8517,12 +7834,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8537,12 +7854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62325</t>
+          <t>60459</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94315</t>
+          <t>91555</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8552,12 +7869,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +7897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19235</t>
+          <t>18423</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38569</t>
+          <t>39299</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8595,12 +7912,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8615,12 +7932,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27204</t>
+          <t>26554</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>50109</t>
+          <t>48571</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8630,12 +7947,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8650,12 +7967,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>50681</t>
+          <t>49512</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>81468</t>
+          <t>80177</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8665,12 +7982,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8010,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46364</t>
+          <t>47003</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>72951</t>
+          <t>74347</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8708,12 +8025,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8728,12 +8045,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>41815</t>
+          <t>42011</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>66725</t>
+          <t>66234</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8743,12 +8060,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8763,12 +8080,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>95605</t>
+          <t>95953</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>132522</t>
+          <t>133663</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8778,12 +8095,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8123,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29737</t>
+          <t>30283</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>53762</t>
+          <t>54046</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8821,12 +8138,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8841,12 +8158,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>23458</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45214</t>
+          <t>45346</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8856,12 +8173,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8876,12 +8193,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>59922</t>
+          <t>58212</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>90181</t>
+          <t>92053</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8891,12 +8208,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8236,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>29890</t>
+          <t>29446</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>52449</t>
+          <t>53119</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8934,12 +8251,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8954,12 +8271,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>32981</t>
+          <t>33700</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8969,12 +8286,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8989,12 +8306,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>50176</t>
+          <t>49774</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>78914</t>
+          <t>78856</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9004,12 +8321,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -9129,7 +8446,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9139,107 +8456,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>81523</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63831</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102604</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>90677</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72978</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>110604</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>161</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>172200</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>146507</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197547</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -9252,107 +8569,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>130</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>137436</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>116065</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>161761</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>128</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126672</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>107928</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>148090</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>264108</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>231851</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>294003</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -9365,107 +8682,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>328</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>357915</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325332</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>393512</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>227</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>230374</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>206850</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>261346</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>555</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>588290</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>547285</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>635151</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -9478,107 +8795,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>343</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>363417</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332091</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>397521</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>270</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>274543</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>247959</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>302262</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>613</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>637961</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>597697</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>682087</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -9591,107 +8908,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>447</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>482031</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>447229</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>520952</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>301</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>313952</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284399</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>342214</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>748</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>795983</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>750530</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>848189</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -9704,804 +9021,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>81523</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>65168</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>101431</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>90677</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>73689</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>110591</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>7,11%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>172200</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>146511</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>198469</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Solo alguna vez</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>137436</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>116073</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>162466</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>9,66%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>11,42%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>126672</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>105796</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>147884</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>12,22%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>14,27%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>264108</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>236031</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>300333</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>10,74%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>12,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>357915</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>327380</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>391865</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>25,16%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>23,02%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>27,55%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>230374</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>202892</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>257840</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>22,23%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>19,58%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>24,88%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>588290</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>545455</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>632762</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>22,19%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>25,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>363417</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>327511</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>397596</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>25,55%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>23,03%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>27,95%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>274543</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>244674</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>301895</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>26,49%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>23,61%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>29,13%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>637961</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>591179</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>680178</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>25,95%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>24,05%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>447</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>482031</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>444873</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>518906</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>33,89%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>31,28%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>36,48%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>313952</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>286053</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>345263</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>30,3%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>27,61%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>33,32%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>748</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>795983</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>749943</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>845585</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>32,38%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>30,5%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>34,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2335</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>

--- a/data/trans_orig/P6713-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6713-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11061</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>15694</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11164</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11925</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17518</t>
+          <t>18107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37233</t>
+          <t>37921</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63671</t>
+          <t>64135</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>10578</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27369</t>
+          <t>28814</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52085</t>
+          <t>52787</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85565</t>
+          <t>85303</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38016</t>
+          <t>39791</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64945</t>
+          <t>66865</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28029</t>
+          <t>28437</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51672</t>
+          <t>54385</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75402</t>
+          <t>74715</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111698</t>
+          <t>111425</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172617</t>
+          <t>173905</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>206989</t>
+          <t>206765</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113484</t>
+          <t>114437</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>142971</t>
+          <t>143065</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296446</t>
+          <t>294735</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>341667</t>
+          <t>338936</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,31%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12311</t>
+          <t>13193</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17456</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20577</t>
+          <t>20514</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18839</t>
+          <t>19207</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>11934</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32850</t>
+          <t>31827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29394</t>
+          <t>28725</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55282</t>
+          <t>53273</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25574</t>
+          <t>26277</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49021</t>
+          <t>48509</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60053</t>
+          <t>60151</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>95500</t>
+          <t>95217</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53811</t>
+          <t>53442</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83625</t>
+          <t>84773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31448</t>
+          <t>31449</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55171</t>
+          <t>55444</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91193</t>
+          <t>91166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129336</t>
+          <t>129964</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115643</t>
+          <t>115837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150090</t>
+          <t>151195</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58222</t>
+          <t>59281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85643</t>
+          <t>85750</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>184450</t>
+          <t>184781</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>229274</t>
+          <t>226470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>53,63%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18322</t>
+          <t>17558</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25207</t>
+          <t>23784</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10611</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>11524</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30600</t>
+          <t>30065</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35906</t>
+          <t>35784</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61392</t>
+          <t>61349</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12963</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30144</t>
+          <t>29937</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>53533</t>
+          <t>52705</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84311</t>
+          <t>81416</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59361</t>
+          <t>58629</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88390</t>
+          <t>86625</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13318</t>
+          <t>13490</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29691</t>
+          <t>30014</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77728</t>
+          <t>79011</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111446</t>
+          <t>111242</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>121554</t>
+          <t>121673</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>157389</t>
+          <t>155434</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50561</t>
+          <t>49772</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71368</t>
+          <t>70712</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>179612</t>
+          <t>179563</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>218116</t>
+          <t>219504</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,41%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31246</t>
+          <t>30220</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12438</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29670</t>
+          <t>30470</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28017</t>
+          <t>27570</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54222</t>
+          <t>52632</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22329</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46059</t>
+          <t>45393</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26554</t>
+          <t>27762</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37196</t>
+          <t>36780</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>65615</t>
+          <t>66194</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>95752</t>
+          <t>94806</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>132555</t>
+          <t>132951</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66983</t>
+          <t>67911</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>98824</t>
+          <t>99962</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>170355</t>
+          <t>171078</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>219152</t>
+          <t>217581</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>83620</t>
+          <t>84169</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120794</t>
+          <t>121537</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53748</t>
+          <t>51815</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81332</t>
+          <t>81543</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>145143</t>
+          <t>145227</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>192783</t>
+          <t>192464</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>142048</t>
+          <t>143222</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>182691</t>
+          <t>183293</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>94299</t>
+          <t>92665</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>127305</t>
+          <t>127906</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>246152</t>
+          <t>246000</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>298372</t>
+          <t>299756</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,37%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17333</t>
+          <t>16931</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36895</t>
+          <t>35534</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18226</t>
+          <t>17828</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>36904</t>
+          <t>37076</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>40470</t>
+          <t>40385</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>66800</t>
+          <t>69728</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>21309</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18249</t>
+          <t>17490</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38455</t>
+          <t>37697</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27145</t>
+          <t>28247</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>52876</t>
+          <t>53318</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29088</t>
+          <t>29103</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>52084</t>
+          <t>51545</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31730</t>
+          <t>31032</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>54307</t>
+          <t>52177</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>65920</t>
+          <t>64780</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>98726</t>
+          <t>97416</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21265</t>
+          <t>21616</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41713</t>
+          <t>41565</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21039</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>39382</t>
+          <t>39340</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>48428</t>
+          <t>46223</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>76147</t>
+          <t>75456</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31878</t>
+          <t>31631</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>54611</t>
+          <t>53628</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>38899</t>
+          <t>39721</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>64655</t>
+          <t>63208</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>76448</t>
+          <t>77799</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>109478</t>
+          <t>110815</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>44843</t>
+          <t>45365</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>76887</t>
+          <t>76903</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>46453</t>
+          <t>45423</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>76194</t>
+          <t>77776</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>96706</t>
+          <t>99184</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>139908</t>
+          <t>143265</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>59406</t>
+          <t>59952</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>95850</t>
+          <t>95520</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>49205</t>
+          <t>48629</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>80445</t>
+          <t>82204</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>114879</t>
+          <t>116201</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>164835</t>
+          <t>165514</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>259390</t>
+          <t>257683</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>319812</t>
+          <t>321132</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>173678</t>
+          <t>174840</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>224700</t>
+          <t>227362</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>449396</t>
+          <t>443412</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>530917</t>
+          <t>529327</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>290681</t>
+          <t>293432</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>357649</t>
+          <t>356761</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>173052</t>
+          <t>174130</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>226030</t>
+          <t>225532</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>482769</t>
+          <t>483511</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>562307</t>
+          <t>568824</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>629882</t>
+          <t>623768</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>707062</t>
+          <t>701651</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>392031</t>
+          <t>391152</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>455033</t>
+          <t>453425</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1040461</t>
+          <t>1032744</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1144728</t>
+          <t>1139157</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>898</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11290</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24040</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22109</t>
+          <t>22611</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>18269</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38973</t>
+          <t>39632</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>39373</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65410</t>
+          <t>67049</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>18916</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39789</t>
+          <t>37681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62601</t>
+          <t>64143</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96841</t>
+          <t>97586</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47212</t>
+          <t>47697</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76270</t>
+          <t>76458</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40966</t>
+          <t>40718</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66281</t>
+          <t>65411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94750</t>
+          <t>95305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134371</t>
+          <t>133125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>134181</t>
+          <t>130705</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>167056</t>
+          <t>166718</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102416</t>
+          <t>103240</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>132076</t>
+          <t>132016</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>246302</t>
+          <t>246115</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>292431</t>
+          <t>291897</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,27%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15886</t>
+          <t>16727</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15258</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>23976</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14544</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32301</t>
+          <t>32647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>32386</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33991</t>
+          <t>33642</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59579</t>
+          <t>57385</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41007</t>
+          <t>39543</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70107</t>
+          <t>69589</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41181</t>
+          <t>42126</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66908</t>
+          <t>67406</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>92610</t>
+          <t>90784</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>129466</t>
+          <t>129595</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53922</t>
+          <t>53591</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83518</t>
+          <t>82318</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38087</t>
+          <t>37845</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61894</t>
+          <t>62871</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99819</t>
+          <t>98782</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>139606</t>
+          <t>134846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76168</t>
+          <t>76023</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107510</t>
+          <t>108443</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44362</t>
+          <t>43694</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70077</t>
+          <t>68584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125485</t>
+          <t>128246</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>167997</t>
+          <t>170054</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14748</t>
+          <t>15552</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22336</t>
+          <t>21531</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>10521</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11151</t>
+          <t>10998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28156</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41625</t>
+          <t>41050</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68630</t>
+          <t>68034</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5645</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>17154</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48746</t>
+          <t>51621</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79129</t>
+          <t>79930</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51416</t>
+          <t>50409</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78096</t>
+          <t>78722</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>14460</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29499</t>
+          <t>29317</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70652</t>
+          <t>70716</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101565</t>
+          <t>101464</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67909</t>
+          <t>65698</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96443</t>
+          <t>94916</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37566</t>
+          <t>37657</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>91028</t>
+          <t>93750</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>127875</t>
+          <t>126640</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29349</t>
+          <t>30339</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54976</t>
+          <t>56751</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20741</t>
+          <t>20286</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41738</t>
+          <t>42259</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54031</t>
+          <t>55299</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86699</t>
+          <t>88204</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48197</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>74969</t>
+          <t>75319</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37454</t>
+          <t>37287</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>63043</t>
+          <t>63420</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>90144</t>
+          <t>91864</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>130466</t>
+          <t>131812</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>119612</t>
+          <t>119849</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>161901</t>
+          <t>160153</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>69117</t>
+          <t>69092</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>100802</t>
+          <t>100730</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>198684</t>
+          <t>198249</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>247280</t>
+          <t>250174</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>110008</t>
+          <t>110823</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>149005</t>
+          <t>149770</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99850</t>
+          <t>101346</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>134581</t>
+          <t>134674</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>221697</t>
+          <t>222087</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>275206</t>
+          <t>272249</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>98208</t>
+          <t>98739</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>136338</t>
+          <t>138931</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74983</t>
+          <t>71359</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>107777</t>
+          <t>103943</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>182305</t>
+          <t>180441</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>233027</t>
+          <t>232431</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37528</t>
+          <t>36303</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39917</t>
+          <t>38097</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63694</t>
+          <t>62331</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60459</t>
+          <t>61811</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>91555</t>
+          <t>94320</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -7897,12 +7897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>17989</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>39299</t>
+          <t>37539</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26554</t>
+          <t>26436</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>48571</t>
+          <t>47704</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7967,12 +7967,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49512</t>
+          <t>51364</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>80177</t>
+          <t>79966</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7982,12 +7982,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8010,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>47003</t>
+          <t>47409</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>74347</t>
+          <t>72228</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>42011</t>
+          <t>40865</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>66234</t>
+          <t>66452</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8060,47 +8060,47 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
+          <t>33,63%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>112765</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>93559</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>131267</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>23,89%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>33,52%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>112765</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>95953</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>133663</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>24,5%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -8123,12 +8123,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30283</t>
+          <t>29201</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>54046</t>
+          <t>52400</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8158,12 +8158,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24401</t>
+          <t>23807</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45346</t>
+          <t>44790</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>58212</t>
+          <t>58717</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>92053</t>
+          <t>90629</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -8236,12 +8236,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>29446</t>
+          <t>29823</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>53119</t>
+          <t>53249</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8251,12 +8251,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>14884</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>33700</t>
+          <t>32804</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>49774</t>
+          <t>48485</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>78856</t>
+          <t>80753</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>63831</t>
+          <t>66025</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>102604</t>
+          <t>101795</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>72978</t>
+          <t>73703</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>110604</t>
+          <t>109372</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>146507</t>
+          <t>149224</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>197547</t>
+          <t>200778</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>116065</t>
+          <t>116574</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>161761</t>
+          <t>159448</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>107928</t>
+          <t>107803</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>148090</t>
+          <t>149395</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>231851</t>
+          <t>231594</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>294003</t>
+          <t>295682</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -8692,12 +8692,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>325332</t>
+          <t>323701</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>393512</t>
+          <t>388731</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8727,12 +8727,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>206850</t>
+          <t>204711</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>261346</t>
+          <t>256991</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>547285</t>
+          <t>546532</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>635151</t>
+          <t>632433</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -8805,12 +8805,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>332091</t>
+          <t>331235</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>397521</t>
+          <t>398886</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>247959</t>
+          <t>247652</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>302262</t>
+          <t>303494</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>597697</t>
+          <t>592783</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>682087</t>
+          <t>682972</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -8918,12 +8918,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>447229</t>
+          <t>444076</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>520952</t>
+          <t>517126</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>284399</t>
+          <t>283890</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>342214</t>
+          <t>346286</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>750530</t>
+          <t>752084</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>848189</t>
+          <t>845447</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
